--- a/AAII_Financials/Yearly/OVV_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/OVV_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>OVV</t>
   </si>
@@ -656,183 +656,195 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10883000</v>
+      </c>
+      <c r="E8" s="3">
         <v>12464000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8658000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6087000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6726000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5939000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4443000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3193000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4422000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8019000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5858000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5160000</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3934000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5108000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3788000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2038000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1922000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1701000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1406000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1283000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1190000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2059000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1434000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1248000</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>6949000</v>
+      </c>
+      <c r="E10" s="3">
         <v>7356000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4870000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4049000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4804000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4238000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3037000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1910000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3232000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5960000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4424000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3912000</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -848,8 +860,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -886,9 +899,12 @@
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -925,87 +941,96 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>47000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>14000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5670000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>168000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-5000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-404000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1396000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>6473000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>21000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4695000</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1825000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1113000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1190000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1834000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2015000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1272000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>833000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>859000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1488000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1745000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1565000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1956000</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1018,86 +1043,93 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8019000</v>
+      </c>
+      <c r="E17" s="3">
         <v>8658000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7139000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>11484000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6158000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4240000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2971000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4741000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10750000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5759000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4989000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9576000</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2864000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3806000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1519000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5397000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>568000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1699000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1472000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1548000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6328000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2260000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>869000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4416000</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1113,203 +1145,219 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>18000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>60000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>38000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>129000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-253000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>245000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>310000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1092000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2990000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-336000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>59000</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4690000</v>
+      </c>
+      <c r="E21" s="3">
         <v>4937000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2769000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3525000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2712000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2718000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2550000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-379000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5932000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6995000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2098000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2401000</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>355000</v>
+      </c>
+      <c r="E22" s="3">
         <v>264000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>340000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>371000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>382000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>283000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>287000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>382000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>590000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>621000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>545000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>474000</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2510000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3560000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1239000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5730000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>315000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1163000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1430000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1620000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8010000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4629000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-12000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4831000</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>425000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-77000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-177000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>367000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>81000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>94000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>276000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-676000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-2845000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1203000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-248000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-2037000</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1346,87 +1394,96 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2085000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3637000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1416000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6097000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>234000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1069000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1154000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-944000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5165000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3426000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>236000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2794000</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2085000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3637000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1416000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6097000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>234000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1069000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1154000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-944000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5165000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3392000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>236000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2794000</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1463,9 +1520,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1484,11 +1544,11 @@
       <c r="H29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="3">
         <v>-327000</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1502,9 +1562,12 @@
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1541,9 +1604,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1580,87 +1646,96 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-18000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-60000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-38000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-129000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>253000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-245000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-310000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1092000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2990000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>336000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-59000</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2085000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3637000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1416000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6097000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>234000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1069000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>827000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-944000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5165000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3392000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>236000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2794000</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1697,92 +1772,101 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2085000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3637000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1416000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6097000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>234000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1069000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>827000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-944000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5165000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3392000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>236000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2794000</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1798,8 +1882,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1815,47 +1900,51 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>195000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>190000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1058000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>719000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>834000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>271000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>338000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2566000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3271000</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1892,48 +1981,54 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1345000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1529000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1296000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1139000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1442000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1005000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1289000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1060000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1571000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1726000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2408000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2332000</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1970,204 +2065,222 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>328000</v>
+      </c>
+      <c r="E45" s="3">
         <v>161000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>96000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>98000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>237000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>613000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>263000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>29000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>410000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>797000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>304000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>875000</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1676000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1695000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1587000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1247000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1869000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2676000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2271000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1923000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1607000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2861000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4290000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5477000</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E47" s="3">
         <v>79000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>91000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>94000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>109000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>101000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>98000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>97000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>231000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>346000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>468000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>810000</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15534000</v>
+      </c>
+      <c r="E48" s="3">
         <v>10338000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9690000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10441000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>16238000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8972000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8954000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8139000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>58301000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>18015000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10035000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>19502000</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2599000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2584000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2628000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2625000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2611000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2553000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2609000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2779000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2790000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2917000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1644000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1725000</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2204,9 +2317,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2243,48 +2359,54 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E52" s="3">
         <v>360000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>59000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>62000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>660000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1042000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1335000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1715000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1425000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>482000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1737000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2519000</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2321,48 +2443,54 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19987000</v>
+      </c>
+      <c r="E54" s="3">
         <v>15056000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14055000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14469000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>21487000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>15344000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15267000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14653000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15614000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>24621000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>17648000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>18700000</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2378,8 +2506,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2395,242 +2524,261 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>835000</v>
+      </c>
+      <c r="E57" s="3">
         <v>709000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>482000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>502000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>355000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>233000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>258000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>240000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1565000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>428000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2160000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>417000</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>291000</v>
+      </c>
+      <c r="E58" s="3">
         <v>399000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>600000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>89000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>584000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>79000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>59000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>54000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>59000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1066000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>507000</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1686000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1672000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2260000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1321000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1989000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1199000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1321000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1263000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1025000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1919000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1621000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1924000</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2812000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2780000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2748000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2423000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2433000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2016000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1658000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1562000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1333000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2406000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2952000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2612000</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5473000</v>
+      </c>
+      <c r="E61" s="3">
         <v>3204000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4819000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6406000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7095000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3909000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4492000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4502000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5333000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7813000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6668000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7244000</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1332000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1383000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1414000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1803000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2030000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1972000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2389000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2463000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4403000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4717000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2881000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5987000</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2667,9 +2815,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2706,9 +2857,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2745,48 +2899,54 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9617000</v>
+      </c>
+      <c r="E66" s="3">
         <v>7367000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8981000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10632000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11558000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7897000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8539000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8527000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9447000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14936000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12501000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13405000</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2802,8 +2962,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2840,9 +3001,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2879,9 +3043,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2918,9 +3085,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2957,48 +3127,54 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>697000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1081000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-4479000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-5773000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>421000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>435000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-429000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1198000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-202000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5188000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2003000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2261000</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3035,9 +3211,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3074,9 +3253,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3113,48 +3295,54 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10370000</v>
+      </c>
+      <c r="E76" s="3">
         <v>7689000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5074000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3837000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9930000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7447000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6728000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6126000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6167000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9685000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5147000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5295000</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3191,92 +3379,101 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2085000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3637000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1416000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6097000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>234000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1069000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>827000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-944000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5165000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3392000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>236000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2794000</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3292,47 +3489,51 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1825000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1113000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1190000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1834000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2015000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1272000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>833000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>859000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1488000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1745000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1565000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1956000</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3369,9 +3570,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3408,9 +3612,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3447,9 +3654,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3486,9 +3696,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3525,48 +3738,54 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4167000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3866000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3129000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1895000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2921000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2300000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1050000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>625000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1681000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2667000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2289000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3107000</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3582,47 +3801,51 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2744000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1831000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1519000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1736000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2626000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1975000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1796000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1132000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2232000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2526000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2712000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3476000</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3659,9 +3882,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3698,48 +3924,54 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5519000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1786000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-525000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1864000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2556000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1555000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1037000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-29000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-665000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4729000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1895000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>361000</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3755,47 +3987,51 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-307000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-239000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-122000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-97000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-102000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-56000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-57000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-51000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-152000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-202000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-401000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-588000</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3832,9 +4068,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3871,9 +4110,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3910,124 +4152,136 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1359000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2268000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2419000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-206000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1238000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-396000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-139000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-38000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1054000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-39000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-909000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1111000</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2000</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-5000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>5000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-10000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>11000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>5000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-29000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-127000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-98000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>22000</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-190000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>185000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-180000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-868000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>339000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-115000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>563000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-67000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2228000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-613000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2379000</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/OVV_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/OVV_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
   <si>
     <t>OVV</t>
   </si>
@@ -950,8 +950,8 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>93000</v>
       </c>
       <c r="E14" s="3">
         <v>47000</v>

--- a/AAII_Financials/Yearly/OVV_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/OVV_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
   <si>
     <t>OVV</t>
   </si>
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>10883000</v>
+        <v>10661000</v>
       </c>
       <c r="E8" s="3">
-        <v>12464000</v>
+        <v>14263000</v>
       </c>
       <c r="F8" s="3">
-        <v>8658000</v>
+        <v>10468000</v>
       </c>
       <c r="G8" s="3">
-        <v>6087000</v>
+        <v>5509000</v>
       </c>
       <c r="H8" s="3">
-        <v>6726000</v>
+        <v>7013000</v>
       </c>
       <c r="I8" s="3">
-        <v>5939000</v>
+        <v>5457000</v>
       </c>
       <c r="J8" s="3">
-        <v>4443000</v>
+        <v>3892000</v>
       </c>
       <c r="K8" s="3">
         <v>3193000</v>
@@ -765,25 +765,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3934000</v>
+        <v>5696000</v>
       </c>
       <c r="E9" s="3">
-        <v>5108000</v>
+        <v>6985000</v>
       </c>
       <c r="F9" s="3">
-        <v>3788000</v>
+        <v>5485000</v>
       </c>
       <c r="G9" s="3">
-        <v>2038000</v>
+        <v>3646000</v>
       </c>
       <c r="H9" s="3">
-        <v>1922000</v>
+        <v>3587000</v>
       </c>
       <c r="I9" s="3">
-        <v>1701000</v>
+        <v>2784000</v>
       </c>
       <c r="J9" s="3">
-        <v>1406000</v>
+        <v>2251000</v>
       </c>
       <c r="K9" s="3">
         <v>1283000</v>
@@ -807,25 +807,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>6949000</v>
+        <v>4965000</v>
       </c>
       <c r="E10" s="3">
-        <v>7356000</v>
+        <v>7278000</v>
       </c>
       <c r="F10" s="3">
-        <v>4870000</v>
+        <v>4983000</v>
       </c>
       <c r="G10" s="3">
-        <v>4049000</v>
+        <v>1863000</v>
       </c>
       <c r="H10" s="3">
-        <v>4804000</v>
+        <v>3426000</v>
       </c>
       <c r="I10" s="3">
-        <v>4238000</v>
+        <v>2673000</v>
       </c>
       <c r="J10" s="3">
-        <v>3037000</v>
+        <v>1641000</v>
       </c>
       <c r="K10" s="3">
         <v>1910000</v>
@@ -951,16 +951,16 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>93000</v>
-      </c>
-      <c r="E14" s="3">
-        <v>47000</v>
-      </c>
-      <c r="F14" s="3">
-        <v>14000</v>
+        <v>76000</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3">
-        <v>5670000</v>
+        <v>5640000</v>
       </c>
       <c r="H14" s="3">
         <v>168000</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8019000</v>
+        <v>7717000</v>
       </c>
       <c r="E17" s="3">
-        <v>8658000</v>
+        <v>10405000</v>
       </c>
       <c r="F17" s="3">
-        <v>7139000</v>
+        <v>8942000</v>
       </c>
       <c r="G17" s="3">
-        <v>11484000</v>
+        <v>5236000</v>
       </c>
       <c r="H17" s="3">
-        <v>6158000</v>
+        <v>6284000</v>
       </c>
       <c r="I17" s="3">
-        <v>4240000</v>
+        <v>3763000</v>
       </c>
       <c r="J17" s="3">
-        <v>2971000</v>
+        <v>2818000</v>
       </c>
       <c r="K17" s="3">
         <v>4741000</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2864000</v>
+        <v>2944000</v>
       </c>
       <c r="E18" s="3">
-        <v>3806000</v>
+        <v>3858000</v>
       </c>
       <c r="F18" s="3">
-        <v>1519000</v>
+        <v>1526000</v>
       </c>
       <c r="G18" s="3">
-        <v>-5397000</v>
+        <v>273000</v>
       </c>
       <c r="H18" s="3">
-        <v>568000</v>
+        <v>729000</v>
       </c>
       <c r="I18" s="3">
-        <v>1699000</v>
+        <v>1694000</v>
       </c>
       <c r="J18" s="3">
-        <v>1472000</v>
+        <v>1074000</v>
       </c>
       <c r="K18" s="3">
         <v>-1548000</v>
@@ -1152,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1000</v>
+        <v>14000</v>
       </c>
       <c r="E20" s="3">
-        <v>18000</v>
+        <v>-13000</v>
       </c>
       <c r="F20" s="3">
-        <v>60000</v>
+        <v>-53000</v>
       </c>
       <c r="G20" s="3">
-        <v>38000</v>
+        <v>-8000</v>
       </c>
       <c r="H20" s="3">
-        <v>129000</v>
+        <v>-136000</v>
       </c>
       <c r="I20" s="3">
-        <v>-253000</v>
+        <v>185000</v>
       </c>
       <c r="J20" s="3">
-        <v>245000</v>
+        <v>-315000</v>
       </c>
       <c r="K20" s="3">
         <v>310000</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4690000</v>
+        <v>4755000</v>
       </c>
       <c r="E21" s="3">
-        <v>4937000</v>
+        <v>4984000</v>
       </c>
       <c r="F21" s="3">
         <v>2769000</v>
       </c>
       <c r="G21" s="3">
-        <v>-3525000</v>
+        <v>2115000</v>
       </c>
       <c r="H21" s="3">
-        <v>2712000</v>
+        <v>2880000</v>
       </c>
       <c r="I21" s="3">
-        <v>2718000</v>
+        <v>2781000</v>
       </c>
       <c r="J21" s="3">
-        <v>2550000</v>
+        <v>2222000</v>
       </c>
       <c r="K21" s="3">
         <v>-379000</v>
@@ -1239,7 +1239,7 @@
         <v>355000</v>
       </c>
       <c r="E22" s="3">
-        <v>264000</v>
+        <v>311000</v>
       </c>
       <c r="F22" s="3">
         <v>340000</v>
@@ -1251,10 +1251,10 @@
         <v>382000</v>
       </c>
       <c r="I22" s="3">
-        <v>283000</v>
+        <v>351000</v>
       </c>
       <c r="J22" s="3">
-        <v>287000</v>
+        <v>363000</v>
       </c>
       <c r="K22" s="3">
         <v>382000</v>
@@ -1338,7 +1338,7 @@
         <v>94000</v>
       </c>
       <c r="J24" s="3">
-        <v>276000</v>
+        <v>603000</v>
       </c>
       <c r="K24" s="3">
         <v>-676000</v>
@@ -1422,7 +1422,7 @@
         <v>1069000</v>
       </c>
       <c r="J26" s="3">
-        <v>1154000</v>
+        <v>827000</v>
       </c>
       <c r="K26" s="3">
         <v>-944000</v>
@@ -1464,7 +1464,7 @@
         <v>1069000</v>
       </c>
       <c r="J27" s="3">
-        <v>1154000</v>
+        <v>827000</v>
       </c>
       <c r="K27" s="3">
         <v>-944000</v>
@@ -1529,26 +1529,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-327000</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1000</v>
+        <v>-14000</v>
       </c>
       <c r="E32" s="3">
-        <v>-18000</v>
+        <v>13000</v>
       </c>
       <c r="F32" s="3">
-        <v>-60000</v>
+        <v>53000</v>
       </c>
       <c r="G32" s="3">
-        <v>-38000</v>
+        <v>8000</v>
       </c>
       <c r="H32" s="3">
-        <v>-129000</v>
+        <v>136000</v>
       </c>
       <c r="I32" s="3">
-        <v>253000</v>
+        <v>-185000</v>
       </c>
       <c r="J32" s="3">
-        <v>-245000</v>
+        <v>315000</v>
       </c>
       <c r="K32" s="3">
         <v>-310000</v>
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>59000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>70000</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>67000</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>41000</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>37000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2032,26 +2032,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2075,25 +2075,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>328000</v>
+        <v>214000</v>
       </c>
       <c r="E45" s="3">
-        <v>161000</v>
+        <v>53000</v>
       </c>
       <c r="F45" s="3">
-        <v>96000</v>
+        <v>1000</v>
       </c>
       <c r="G45" s="3">
-        <v>98000</v>
+        <v>37000</v>
       </c>
       <c r="H45" s="3">
-        <v>237000</v>
+        <v>148000</v>
       </c>
       <c r="I45" s="3">
-        <v>613000</v>
+        <v>554000</v>
       </c>
       <c r="J45" s="3">
-        <v>263000</v>
+        <v>205000</v>
       </c>
       <c r="K45" s="3">
         <v>29000</v>
@@ -2159,25 +2159,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>63000</v>
+        <v>26000</v>
       </c>
       <c r="E47" s="3">
-        <v>79000</v>
+        <v>21000</v>
       </c>
       <c r="F47" s="3">
-        <v>91000</v>
+        <v>27000</v>
       </c>
       <c r="G47" s="3">
-        <v>94000</v>
+        <v>30000</v>
       </c>
       <c r="H47" s="3">
-        <v>109000</v>
+        <v>28000</v>
       </c>
       <c r="I47" s="3">
-        <v>101000</v>
+        <v>22000</v>
       </c>
       <c r="J47" s="3">
-        <v>98000</v>
+        <v>26000</v>
       </c>
       <c r="K47" s="3">
         <v>97000</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>115000</v>
+        <v>55000</v>
       </c>
       <c r="E52" s="3">
-        <v>360000</v>
+        <v>103000</v>
       </c>
       <c r="F52" s="3">
-        <v>59000</v>
+        <v>81000</v>
       </c>
       <c r="G52" s="3">
-        <v>62000</v>
+        <v>81000</v>
       </c>
       <c r="H52" s="3">
-        <v>660000</v>
+        <v>134000</v>
       </c>
       <c r="I52" s="3">
-        <v>1042000</v>
+        <v>277000</v>
       </c>
       <c r="J52" s="3">
-        <v>1335000</v>
+        <v>357000</v>
       </c>
       <c r="K52" s="3">
         <v>1715000</v>
@@ -2531,16 +2531,16 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>835000</v>
+        <v>586000</v>
       </c>
       <c r="E57" s="3">
-        <v>709000</v>
+        <v>436000</v>
       </c>
       <c r="F57" s="3">
-        <v>482000</v>
+        <v>328000</v>
       </c>
       <c r="G57" s="3">
-        <v>502000</v>
+        <v>306000</v>
       </c>
       <c r="H57" s="3">
         <v>355000</v>
@@ -2573,19 +2573,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>291000</v>
+        <v>378000</v>
       </c>
       <c r="E58" s="3">
-        <v>399000</v>
+        <v>475000</v>
       </c>
       <c r="F58" s="3">
-        <v>6000</v>
+        <v>68000</v>
       </c>
       <c r="G58" s="3">
-        <v>600000</v>
+        <v>668000</v>
       </c>
       <c r="H58" s="3">
-        <v>89000</v>
+        <v>167000</v>
       </c>
       <c r="I58" s="3">
         <v>584000</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1686000</v>
+        <v>574000</v>
       </c>
       <c r="E59" s="3">
-        <v>1672000</v>
+        <v>422000</v>
       </c>
       <c r="F59" s="3">
-        <v>2260000</v>
+        <v>1036000</v>
       </c>
       <c r="G59" s="3">
-        <v>1321000</v>
+        <v>425000</v>
       </c>
       <c r="H59" s="3">
-        <v>1989000</v>
+        <v>733000</v>
       </c>
       <c r="I59" s="3">
-        <v>1199000</v>
+        <v>393000</v>
       </c>
       <c r="J59" s="3">
-        <v>1321000</v>
+        <v>606000</v>
       </c>
       <c r="K59" s="3">
         <v>1263000</v>
@@ -2669,7 +2669,7 @@
         <v>2423000</v>
       </c>
       <c r="H60" s="3">
-        <v>2433000</v>
+        <v>2432000</v>
       </c>
       <c r="I60" s="3">
         <v>2016000</v>
@@ -2699,19 +2699,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>5473000</v>
+        <v>6305000</v>
       </c>
       <c r="E61" s="3">
-        <v>3204000</v>
+        <v>4018000</v>
       </c>
       <c r="F61" s="3">
-        <v>4819000</v>
+        <v>5708000</v>
       </c>
       <c r="G61" s="3">
-        <v>6406000</v>
+        <v>7344000</v>
       </c>
       <c r="H61" s="3">
-        <v>7095000</v>
+        <v>8072000</v>
       </c>
       <c r="I61" s="3">
         <v>3909000</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1332000</v>
+        <v>316000</v>
       </c>
       <c r="E62" s="3">
-        <v>1383000</v>
+        <v>312000</v>
       </c>
       <c r="F62" s="3">
-        <v>1414000</v>
+        <v>417000</v>
       </c>
       <c r="G62" s="3">
-        <v>1803000</v>
+        <v>716000</v>
       </c>
       <c r="H62" s="3">
-        <v>2030000</v>
+        <v>717000</v>
       </c>
       <c r="I62" s="3">
-        <v>1972000</v>
+        <v>1840000</v>
       </c>
       <c r="J62" s="3">
-        <v>2389000</v>
+        <v>2239000</v>
       </c>
       <c r="K62" s="3">
         <v>2463000</v>
@@ -2921,7 +2921,7 @@
         <v>10632000</v>
       </c>
       <c r="H66" s="3">
-        <v>11558000</v>
+        <v>11557000</v>
       </c>
       <c r="I66" s="3">
         <v>7897000</v>
@@ -3820,13 +3820,13 @@
         <v>-1736000</v>
       </c>
       <c r="H91" s="3">
-        <v>-2626000</v>
+        <v>-2691000</v>
       </c>
       <c r="I91" s="3">
-        <v>-1975000</v>
+        <v>-1992000</v>
       </c>
       <c r="J91" s="3">
-        <v>-1796000</v>
+        <v>-1850000</v>
       </c>
       <c r="K91" s="3">
         <v>-1132000</v>
@@ -3994,25 +3994,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-307000</v>
+        <v>307000</v>
       </c>
       <c r="E96" s="3">
-        <v>-239000</v>
+        <v>239000</v>
       </c>
       <c r="F96" s="3">
-        <v>-122000</v>
+        <v>122000</v>
       </c>
       <c r="G96" s="3">
-        <v>-97000</v>
+        <v>97000</v>
       </c>
       <c r="H96" s="3">
-        <v>-102000</v>
+        <v>102000</v>
       </c>
       <c r="I96" s="3">
-        <v>-56000</v>
+        <v>56000</v>
       </c>
       <c r="J96" s="3">
-        <v>-57000</v>
+        <v>57000</v>
       </c>
       <c r="K96" s="3">
         <v>-51000</v>
@@ -4209,8 +4209,8 @@
       <c r="E101" s="3">
         <v>-2000</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G101" s="3">
         <v>-5000</v>

--- a/AAII_Financials/Yearly/OVV_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/OVV_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>OVV</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8943000</v>
+      </c>
+      <c r="E8" s="3">
         <v>10661000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14263000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>10468000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5509000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7013000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5457000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3892000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3193000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4422000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8019000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5858000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5160000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4346000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5696000</v>
       </c>
-      <c r="E9" s="3">
-        <v>6985000</v>
-      </c>
       <c r="F9" s="3">
+        <v>7058000</v>
+      </c>
+      <c r="G9" s="3">
         <v>5485000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3646000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3587000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2784000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2251000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1283000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1190000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2059000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1434000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1248000</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4597000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4965000</v>
       </c>
-      <c r="E10" s="3">
-        <v>7278000</v>
-      </c>
       <c r="F10" s="3">
+        <v>7205000</v>
+      </c>
+      <c r="G10" s="3">
         <v>4983000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1863000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3426000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2673000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1641000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1910000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3232000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5960000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4424000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3912000</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,14 +960,17 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>76000</v>
+        <v>477000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -959,78 +978,84 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
         <v>5640000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>168000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-5000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-404000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1396000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6473000</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>21000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4695000</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2290000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1825000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1113000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1190000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1834000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2015000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1272000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>833000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>859000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1488000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1745000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1565000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1956000</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7717000</v>
+        <v>6883000</v>
       </c>
       <c r="E17" s="3">
+        <v>7793000</v>
+      </c>
+      <c r="F17" s="3">
         <v>10405000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8942000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5236000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6284000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3763000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2818000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4741000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10750000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5759000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4989000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9576000</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2944000</v>
+        <v>2060000</v>
       </c>
       <c r="E18" s="3">
+        <v>2868000</v>
+      </c>
+      <c r="F18" s="3">
         <v>3858000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1526000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>273000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>729000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1694000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1074000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1548000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6328000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2260000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>869000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4416000</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-173000</v>
+      </c>
+      <c r="E20" s="3">
         <v>14000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-13000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-53000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-8000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-136000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>185000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-315000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>310000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1092000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2990000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-336000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>59000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4755000</v>
+        <v>4523000</v>
       </c>
       <c r="E21" s="3">
+        <v>4679000</v>
+      </c>
+      <c r="F21" s="3">
         <v>4984000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2769000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2115000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2880000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2781000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2222000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-379000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5932000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6995000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2098000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2401000</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>412000</v>
+      </c>
+      <c r="E22" s="3">
         <v>355000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>311000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>340000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>371000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>382000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>351000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>363000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>382000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>590000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>621000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>545000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>474000</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1351000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2510000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3560000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1239000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5730000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>315000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1163000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1430000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1620000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8010000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4629000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-12000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4831000</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>226000</v>
+      </c>
+      <c r="E24" s="3">
         <v>425000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-77000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-177000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>367000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>81000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>94000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>603000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-676000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-2845000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1203000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-248000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2037000</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1125000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2085000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3637000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1416000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-6097000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>234000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1069000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>827000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-944000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5165000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3426000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>236000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2794000</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1125000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2085000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3637000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1416000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6097000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>234000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1069000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>827000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-944000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5165000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3392000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>236000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2794000</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1550,8 +1610,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>173000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-14000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>13000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>53000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>8000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>136000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-185000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>315000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-310000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1092000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2990000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>336000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-59000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1125000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2085000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3637000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1416000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-6097000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>234000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1069000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>827000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-944000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5165000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3392000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>236000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2794000</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1125000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2085000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3637000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1416000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-6097000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>234000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1069000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>827000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-944000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5165000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3392000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>236000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2794000</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,77 +1986,81 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>195000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>190000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1058000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>719000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>834000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>271000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>338000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2566000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3271000</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E42" s="3">
         <v>59000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>70000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>67000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>38000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>41000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>44000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>37000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -1984,51 +2073,57 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1121000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1345000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1529000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1296000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1139000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1442000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1005000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1289000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1060000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1571000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1726000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2408000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2332000</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2053,8 +2148,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2068,219 +2163,237 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E45" s="3">
         <v>214000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>53000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>37000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>148000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>554000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>205000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>29000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>410000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>797000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>304000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>875000</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1369000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1676000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1695000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1587000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1247000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1869000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2676000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2271000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1923000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1607000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2861000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4290000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5477000</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E47" s="3">
         <v>26000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>21000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>27000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>30000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>28000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>22000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>26000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>97000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>231000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>346000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>468000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>810000</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15152000</v>
+      </c>
+      <c r="E48" s="3">
         <v>15534000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10338000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9690000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10441000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>16238000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8972000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8954000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8139000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>58301000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>18015000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10035000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>19502000</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2546000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2599000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2584000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2628000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2625000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2611000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2553000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2609000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2779000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2790000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2917000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1644000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1725000</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>95000</v>
+      </c>
+      <c r="E52" s="3">
         <v>55000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>103000</v>
-      </c>
-      <c r="F52" s="3">
-        <v>81000</v>
       </c>
       <c r="G52" s="3">
         <v>81000</v>
       </c>
       <c r="H52" s="3">
+        <v>81000</v>
+      </c>
+      <c r="I52" s="3">
         <v>134000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>277000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>357000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1715000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1425000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>482000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1737000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2519000</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19254000</v>
+      </c>
+      <c r="E54" s="3">
         <v>19987000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15056000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14055000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14469000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21487000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15344000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>15267000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14653000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15614000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>24621000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>17648000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>18700000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>435000</v>
+      </c>
+      <c r="E57" s="3">
         <v>586000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>436000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>328000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>306000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>355000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>233000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>258000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>240000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1565000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>428000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2160000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>417000</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>690000</v>
+      </c>
+      <c r="E58" s="3">
         <v>378000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>475000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>68000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>668000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>167000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>584000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>79000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>59000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>54000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>59000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1066000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>507000</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>400000</v>
+      </c>
+      <c r="E59" s="3">
         <v>574000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>422000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1036000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>425000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>733000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>393000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>606000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1263000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1025000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1919000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1621000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1924000</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2681000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2812000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2780000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2748000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2423000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2432000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2016000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1658000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1562000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1333000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2406000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2952000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2612000</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5602000</v>
+      </c>
+      <c r="E61" s="3">
         <v>6305000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4018000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5708000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7344000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8072000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3909000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4492000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4502000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5333000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7813000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6668000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7244000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>364000</v>
+      </c>
+      <c r="E62" s="3">
         <v>316000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>312000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>417000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>716000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>717000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1840000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2239000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2463000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4403000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4717000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2881000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5987000</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8923000</v>
+      </c>
+      <c r="E66" s="3">
         <v>9617000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7367000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8981000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10632000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11557000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7897000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8539000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8527000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9447000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14936000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12501000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13405000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1506000</v>
+      </c>
+      <c r="E72" s="3">
         <v>697000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1081000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-4479000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-5773000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>421000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>435000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-429000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1198000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-202000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5188000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2003000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2261000</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10331000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10370000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7689000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5074000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3837000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9930000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7447000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6728000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6126000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6167000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9685000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5147000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5295000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1125000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2085000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3637000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1416000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-6097000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>234000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1069000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>827000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-944000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5165000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3392000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>236000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2794000</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2290000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1825000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1113000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1190000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1834000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2015000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1272000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>833000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>859000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1488000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1745000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1565000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1956000</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3721000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4167000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3866000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3129000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1895000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2921000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2300000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1050000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>625000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1681000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2667000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2289000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3107000</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-2744000</v>
+        <v>-2508000</v>
       </c>
       <c r="E91" s="3">
-        <v>-1831000</v>
+        <v>-3021000</v>
       </c>
       <c r="F91" s="3">
-        <v>-1519000</v>
+        <v>-2117000</v>
       </c>
       <c r="G91" s="3">
+        <v>-1530000</v>
+      </c>
+      <c r="H91" s="3">
         <v>-1736000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2691000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1992000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1850000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1132000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2232000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2526000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2712000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3476000</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2457000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5519000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1786000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-525000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1864000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2556000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1555000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1037000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-29000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-665000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4729000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1895000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>361000</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>316000</v>
+      </c>
+      <c r="E96" s="3">
         <v>307000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>239000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>122000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>97000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>102000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>56000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>57000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-51000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-152000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-202000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-401000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-588000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1231000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1359000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2268000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2419000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-206000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1238000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-396000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-139000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-38000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1054000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-39000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-909000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1111000</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-9000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2000</v>
       </c>
-      <c r="F101" s="3" t="s">
+      <c r="G101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>5000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-10000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>11000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>5000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-29000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-127000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-98000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>22000</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-190000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>185000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-180000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-868000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>339000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-115000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>563000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-67000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2228000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-613000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2379000</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/OVV_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/OVV_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
   <si>
     <t>OVV</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8663000</v>
+      </c>
+      <c r="E8" s="3">
         <v>8943000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10661000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14263000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10468000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5509000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7013000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5457000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3892000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3193000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4422000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8019000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5858000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5160000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4165000</v>
+      </c>
+      <c r="E9" s="3">
         <v>4346000</v>
       </c>
-      <c r="E9" s="3">
-        <v>5696000</v>
-      </c>
       <c r="F9" s="3">
+        <v>5782000</v>
+      </c>
+      <c r="G9" s="3">
         <v>7058000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5485000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3646000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3587000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2784000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2251000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1283000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1190000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2059000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1434000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1248000</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4498000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4597000</v>
       </c>
-      <c r="E10" s="3">
-        <v>4965000</v>
-      </c>
       <c r="F10" s="3">
+        <v>4879000</v>
+      </c>
+      <c r="G10" s="3">
         <v>7205000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4983000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1863000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3426000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2673000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1641000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1910000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3232000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5960000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4424000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3912000</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,8 +886,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,17 +979,20 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>932000</v>
+      </c>
+      <c r="E14" s="3">
         <v>477000</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -981,81 +1000,87 @@
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>5640000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>168000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-5000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-404000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1396000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6473000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>21000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4695000</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2179000</v>
+      </c>
+      <c r="E15" s="3">
         <v>2290000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1825000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1113000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1190000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1834000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2015000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1272000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>833000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>859000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1488000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1745000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1565000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1956000</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6597000</v>
+      </c>
+      <c r="E17" s="3">
         <v>6883000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7793000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10405000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8942000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5236000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6284000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3763000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2818000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4741000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10750000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5759000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4989000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9576000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2066000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2060000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2868000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3858000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1526000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>273000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>729000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1694000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1074000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1548000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6328000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2260000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>869000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4416000</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-173000</v>
       </c>
-      <c r="E20" s="3">
-        <v>14000</v>
-      </c>
       <c r="F20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G20" s="3">
         <v>-13000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-53000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-8000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-136000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>185000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-315000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>310000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1092000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2990000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-336000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>59000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4246000</v>
+      </c>
+      <c r="E21" s="3">
         <v>4523000</v>
       </c>
-      <c r="E21" s="3">
-        <v>4679000</v>
-      </c>
       <c r="F21" s="3">
+        <v>4690000</v>
+      </c>
+      <c r="G21" s="3">
         <v>4984000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2769000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2115000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2880000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2781000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2222000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-379000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-5932000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6995000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2098000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2401000</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>376000</v>
+      </c>
+      <c r="E22" s="3">
         <v>412000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>355000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>311000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>340000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>371000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>382000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>351000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>363000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>382000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>590000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>621000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>545000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>474000</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>770000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1351000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2510000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3560000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1239000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5730000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>315000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1163000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1430000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1620000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8010000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4629000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-12000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4831000</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-472000</v>
+      </c>
+      <c r="E24" s="3">
         <v>226000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>425000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-77000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-177000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>367000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>81000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>94000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>603000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-676000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2845000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1203000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-248000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2037000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1242000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1125000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2085000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3637000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1416000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6097000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>234000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1069000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>827000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-944000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5165000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3426000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>236000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2794000</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1242000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1125000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2085000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3637000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1416000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6097000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>234000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1069000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>827000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-944000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5165000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3392000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>236000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2794000</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1613,8 +1673,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>173000</v>
       </c>
-      <c r="E32" s="3">
-        <v>-14000</v>
-      </c>
       <c r="F32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="G32" s="3">
         <v>13000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>53000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>8000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>136000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-185000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>315000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-310000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1092000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2990000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>336000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-59000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1242000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1125000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2085000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3637000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1416000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6097000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>234000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1069000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>827000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-944000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5165000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3392000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>236000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2794000</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1242000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1125000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2085000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3637000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1416000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6097000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>234000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1069000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>827000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-944000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5165000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3392000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>236000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2794000</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,83 +2072,87 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E41" s="3">
         <v>42000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>195000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>190000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1058000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>719000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>834000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>271000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>338000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2566000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3271000</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>285000</v>
+      </c>
+      <c r="E42" s="3">
         <v>42000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>59000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>70000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>67000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>38000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>41000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>44000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>37000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2076,54 +2165,60 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1061000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1121000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1345000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1529000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1296000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1139000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1442000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1005000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1289000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1060000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1571000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1726000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2408000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2332000</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2151,8 +2246,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2166,234 +2261,252 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>86000</v>
+      </c>
+      <c r="E45" s="3">
         <v>108000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>214000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>53000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>37000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>148000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>554000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>205000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>29000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>410000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>797000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>304000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>875000</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1523000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1369000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1676000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1695000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1587000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1247000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1869000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2676000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2271000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1923000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1607000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2861000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4290000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5477000</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E47" s="3">
         <v>33000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>26000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>21000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>27000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>30000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>28000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>22000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>26000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>97000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>231000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>346000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>468000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>810000</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15431000</v>
+      </c>
+      <c r="E48" s="3">
         <v>15152000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15534000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10338000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9690000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10441000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>16238000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8972000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8954000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8139000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>58301000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>18015000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10035000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>19502000</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2576000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2546000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2599000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2584000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2628000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2625000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2611000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2553000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2609000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2779000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2790000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2917000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1644000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1725000</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E52" s="3">
         <v>95000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>55000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>103000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>81000</v>
       </c>
       <c r="H52" s="3">
         <v>81000</v>
       </c>
       <c r="I52" s="3">
+        <v>81000</v>
+      </c>
+      <c r="J52" s="3">
         <v>134000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>277000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>357000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1715000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1425000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>482000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1737000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2519000</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20390000</v>
+      </c>
+      <c r="E54" s="3">
         <v>19254000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>19987000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15056000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14055000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14469000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>21487000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>15344000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15267000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14653000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>15614000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>24621000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17648000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>18700000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>390000</v>
+      </c>
+      <c r="E57" s="3">
         <v>435000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>586000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>436000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>328000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>306000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>355000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>233000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>258000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>240000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1565000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>428000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2160000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>417000</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>927000</v>
+      </c>
+      <c r="E58" s="3">
         <v>690000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>378000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>475000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>68000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>668000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>167000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>584000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>79000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>59000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>54000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>59000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1066000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>507000</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>406000</v>
+      </c>
+      <c r="E59" s="3">
         <v>400000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>574000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>422000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1036000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>425000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>733000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>393000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>606000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1263000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1025000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1919000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1621000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1924000</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2795000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2681000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2812000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2780000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2748000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2423000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2432000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2016000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1658000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1562000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1333000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2406000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2952000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2612000</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5497000</v>
+      </c>
+      <c r="E61" s="3">
         <v>5602000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6305000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4018000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5708000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7344000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8072000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3909000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4492000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4502000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5333000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7813000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6668000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7244000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>426000</v>
+      </c>
+      <c r="E62" s="3">
         <v>364000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>316000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>312000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>417000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>716000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>717000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1840000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2239000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2463000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4403000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4717000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2881000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5987000</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9195000</v>
+      </c>
+      <c r="E66" s="3">
         <v>8923000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9617000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7367000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8981000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10632000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11557000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7897000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8539000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>8527000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9447000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14936000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12501000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13405000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2440000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1506000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>697000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1081000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-4479000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-5773000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>421000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>435000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-429000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1198000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-202000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5188000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2003000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2261000</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11195000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10331000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10370000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7689000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5074000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3837000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9930000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7447000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6728000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6126000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6167000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9685000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5147000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5295000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1242000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1125000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2085000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3637000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1416000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6097000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>234000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1069000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>827000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-944000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5165000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3392000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>236000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2794000</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2179000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2290000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1825000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1113000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1190000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1834000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2015000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1272000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>833000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>859000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1488000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1745000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1565000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1956000</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3652000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3721000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4167000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3866000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3129000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1895000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2921000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2300000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1050000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>625000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1681000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2667000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2289000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3107000</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4684000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2508000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3021000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2117000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1530000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1736000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2691000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1992000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1850000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1132000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2232000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2526000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2712000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3476000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2884000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2457000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5519000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1786000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-525000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1864000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2556000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1555000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1037000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-29000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-665000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4729000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1895000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>361000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,53 +4453,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>308000</v>
+      </c>
+      <c r="E96" s="3">
         <v>316000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>307000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>239000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>122000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>97000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>102000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>56000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>57000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-51000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-152000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-202000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-401000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-588000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-762000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1231000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1359000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2268000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2419000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-206000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1238000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-396000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-139000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-38000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1054000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-39000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-909000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1111000</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E101" s="3">
         <v>6000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-9000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2000</v>
       </c>
-      <c r="G101" s="3" t="s">
+      <c r="H101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>5000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-10000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>11000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>5000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-29000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-127000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-98000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>22000</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E102" s="3">
         <v>39000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-190000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>185000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-180000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-868000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>339000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-115000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>563000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-67000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2228000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-613000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2379000</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
